--- a/evaluation/evaluation.xlsx
+++ b/evaluation/evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramaw\Documents\master-thesis\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7C0003-CC7D-4DFA-9AB7-6B72CA150791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647D995E-F1DA-4107-B10B-DC137B0AADE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{72E58FE3-2FF7-4DAF-898B-173E722938DB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{72E58FE3-2FF7-4DAF-898B-173E722938DB}"/>
   </bookViews>
   <sheets>
     <sheet name="text2sparql-A-8B" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>exact query as A70B</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -2033,13 +2036,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H21" s="1" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="G21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="3"/>
@@ -2557,7 +2558,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2791,13 +2792,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H21" s="1" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="G21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="3"/>

--- a/evaluation/evaluation.xlsx
+++ b/evaluation/evaluation.xlsx
@@ -8,17 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramaw\Documents\master-thesis\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647D995E-F1DA-4107-B10B-DC137B0AADE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1D8AB0-F6D6-4D88-9332-80462BA59B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{72E58FE3-2FF7-4DAF-898B-173E722938DB}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="3" xr2:uid="{72E58FE3-2FF7-4DAF-898B-173E722938DB}"/>
   </bookViews>
   <sheets>
     <sheet name="text2sparql-A-8B" sheetId="1" r:id="rId1"/>
     <sheet name="text2sparql-AT-8B" sheetId="4" r:id="rId2"/>
     <sheet name="text2sparql-A-70B" sheetId="2" r:id="rId3"/>
     <sheet name="text2sparql-AT-70B" sheetId="5" r:id="rId4"/>
-    <sheet name="triple2text-8B" sheetId="3" r:id="rId5"/>
-    <sheet name="triple2text-70B" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -1389,11 +1387,11 @@
         <v>1</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G21" si="1">C3/(C3+E3)</f>
+        <f t="shared" ref="G3:G20" si="1">C3/(C3+E3)</f>
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H21" si="2">2*(F3*G3)/(F3+G3)</f>
+        <f t="shared" ref="H3:H20" si="2">2*(F3*G3)/(F3+G3)</f>
         <v>1</v>
       </c>
       <c r="I3" s="1">
@@ -2153,11 +2151,11 @@
         <v>1</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G21" si="1">C3/(C3+E3)</f>
+        <f t="shared" ref="G3:G20" si="1">C3/(C3+E3)</f>
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H21" si="2">2*(F3*G3)/(F3+G3)</f>
+        <f t="shared" ref="H3:H20" si="2">2*(F3*G3)/(F3+G3)</f>
         <v>1</v>
       </c>
       <c r="I3" s="1">
@@ -2806,248 +2804,6 @@
         <v>73</v>
       </c>
       <c r="K21" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E96E6BD8-6816-4E74-963F-BDE060A398BE}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97EF2EF6-7376-41B6-8FD5-70762628951E}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
